--- a/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/software_contracts.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/10_vendors_contracts_source/software_contracts.xlsx
@@ -485,20 +485,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2028-11-14</t>
+          <t>2027-12-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.2</v>
+        <v>7.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2027-07-28</t>
+          <t>2027-12-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -535,15 +535,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -560,15 +560,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2027-10-28</t>
+          <t>2027-08-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -585,15 +585,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.3</v>
+        <v>1.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2028-06-21</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -610,20 +610,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2027-12-08</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -635,20 +635,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
@@ -660,15 +660,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.6</v>
+        <v>5.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2027-01-06</t>
+          <t>2027-03-31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -685,20 +685,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2028-11-11</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
@@ -714,16 +714,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
@@ -735,20 +735,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2027-03-13</t>
+          <t>2028-10-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -764,16 +764,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.9</v>
+        <v>3.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2028-07-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
@@ -785,15 +785,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2028-09-08</t>
+          <t>2028-10-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -810,15 +810,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2028-03-06</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -835,20 +835,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.1</v>
+        <v>11.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2027-04-17</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -860,20 +860,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.2</v>
+        <v>9.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2028-12-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
@@ -885,20 +885,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
@@ -910,15 +910,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kyriba</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2028-05-22</t>
+          <t>2028-08-04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -935,20 +935,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2028-03-03</t>
+          <t>2028-03-06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
@@ -960,15 +960,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.3</v>
+        <v>7.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2027-12-04</t>
+          <t>2027-08-01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -985,20 +985,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2027-03-08</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
@@ -1014,16 +1014,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.2</v>
+        <v>7.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2027-02-25</t>
+          <t>2027-09-25</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1035,20 +1035,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2028-12-05</t>
+          <t>2027-09-13</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2027-07-28</t>
+          <t>2027-07-27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1085,15 +1085,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2027-02-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1110,15 +1110,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2028-09-10</t>
+          <t>2028-07-13</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1135,20 +1135,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2027-05-31</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
@@ -1160,20 +1160,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2028-11-09</t>
+          <t>2028-07-09</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
@@ -1185,15 +1185,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.699999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2028-09-15</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1210,15 +1210,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.6</v>
+        <v>10.6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2027-11-18</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1235,20 +1235,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2028-06-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
@@ -1260,20 +1260,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2027-12-08</t>
+          <t>2028-07-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
@@ -1285,20 +1285,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2028-10-31</t>
+          <t>2028-02-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
@@ -1310,20 +1310,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2028-06-23</t>
+          <t>2028-12-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1335,20 +1335,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2027-10-08</t>
+          <t>2028-10-08</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
@@ -1360,20 +1360,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2028-03-01</t>
+          <t>2028-03-16</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
@@ -1385,15 +1385,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1410,20 +1410,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Coupa</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9.5</v>
+        <v>1.6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2028-07-26</t>
+          <t>2027-03-14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Negotiate</t>
+          <t>Auto</t>
         </is>
       </c>
     </row>
@@ -1435,20 +1435,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Coupa</t>
+          <t>Kyriba</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2027-11-25</t>
+          <t>2028-03-31</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
@@ -1460,20 +1460,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7.8</v>
+        <v>2.3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2028-09-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Negotiate</t>
         </is>
       </c>
     </row>
